--- a/sample_grn1.xlsx
+++ b/sample_grn1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\grn_post\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91612AA-A7E8-4A0D-9E1B-81F85C632D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93F631E-6557-49AA-99E8-F2FB9D0683CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Voucher Type</t>
   </si>
@@ -93,12 +93,6 @@
     <t>Main Location</t>
   </si>
   <si>
-    <t>Alu Patra</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
     <t>Tofajul (B)</t>
   </si>
   <si>
@@ -108,23 +102,17 @@
     <t>Okra</t>
   </si>
   <si>
-    <t>A1 Fruits</t>
-  </si>
-  <si>
-    <t>Amla</t>
-  </si>
-  <si>
-    <t>Apple</t>
-  </si>
-  <si>
     <t>Kg</t>
+  </si>
+  <si>
+    <t>Purchase Voucher - 1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,6 +127,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -161,10 +155,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -469,23 +466,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
@@ -537,30 +534,30 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C2" s="2">
         <v>46281</v>
       </c>
       <c r="D2">
         <f>B2</f>
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
         <v>21</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>22</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
       </c>
       <c r="I2">
         <f>B2</f>
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
@@ -574,146 +571,8 @@
       <c r="M2" t="s">
         <v>18</v>
       </c>
-      <c r="N2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>221</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46281</v>
-      </c>
-      <c r="D3">
-        <f t="shared" ref="D3:D5" si="0">B3</f>
-        <v>221</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3">
-        <f t="shared" ref="I3:I5" si="1">B3</f>
-        <v>221</v>
-      </c>
-      <c r="J3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
-        <v>222</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46281</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>222</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4">
-        <f t="shared" si="1"/>
-        <v>222</v>
-      </c>
-      <c r="J4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5">
-        <v>222</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46281</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>222</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5">
-        <f t="shared" si="1"/>
-        <v>222</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" t="s">
-        <v>17</v>
-      </c>
-      <c r="M5" t="s">
-        <v>18</v>
-      </c>
-      <c r="N5" t="s">
-        <v>20</v>
+      <c r="N2" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
